--- a/data/Data_GUT.xlsx
+++ b/data/Data_GUT.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E7418A-7FB2-C145-8402-4FBF60419BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C72F3C-EF01-594E-88EE-1CA272041C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1740" windowWidth="27240" windowHeight="16260" xr2:uid="{C2C97289-876A-D64D-8FE1-EB8CA55BA769}"/>
+    <workbookView xWindow="-30800" yWindow="580" windowWidth="14400" windowHeight="9660" activeTab="1" xr2:uid="{C2C97289-876A-D64D-8FE1-EB8CA55BA769}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -60,6 +61,30 @@
   </si>
   <si>
     <t>Massaged</t>
+  </si>
+  <si>
+    <t>-   `date` : Date of the measurement (DD-MM-YYY format)</t>
+  </si>
+  <si>
+    <t>-   `Heure` : Hour of the measurement (HH-MM format)</t>
+  </si>
+  <si>
+    <t>-   `t` : Number of days since the start of the experiment (range: 0-32)</t>
+  </si>
+  <si>
+    <t>-   `ID` : Identification number of the earthworm (range: 1-10).</t>
+  </si>
+  <si>
+    <t>-   `Weight` : Fresh weight of the earthworm (mg, range 315-817).</t>
+  </si>
+  <si>
+    <t>-   `Handling` :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -   “None” : Nothing special done to the earthworm before measurement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -   “Massaged” : The earthworm is gently massaged to remove the remaining of its gut content before measurement.</t>
   </si>
 </sst>
 </file>
@@ -3378,4 +3403,54 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C60619-54D7-E34F-B869-9772823BFB25}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>